--- a/2026_project/2_data_processed/intermediate_output/pipeline_network_manual_edit.xlsx
+++ b/2026_project/2_data_processed/intermediate_output/pipeline_network_manual_edit.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dutka\MT\AdOpT-NET0_dw\2026_project\2_data_processed\intermediate_output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D7902B0-9B74-4AC9-88C8-820153B8F6DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{317AA9A5-DFC0-412D-9C2A-10F1E24332D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12320" yWindow="3340" windowWidth="12220" windowHeight="7510" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$664</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
@@ -22570,6 +22573,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:K664" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/2026_project/2_data_processed/intermediate_output/pipeline_network_manual_edit.xlsx
+++ b/2026_project/2_data_processed/intermediate_output/pipeline_network_manual_edit.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dutka\MT\AdOpT-NET0_dw\2026_project\2_data_processed\intermediate_output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{317AA9A5-DFC0-412D-9C2A-10F1E24332D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F2BC5DB-0AFD-436A-9358-408F4DDAA438}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$664</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$669</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3459" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3487" uniqueCount="170">
   <si>
     <t>edge_type</t>
   </si>
@@ -505,31 +505,13 @@
     <t>manual_addition</t>
   </si>
   <si>
-    <t>Ä°DÃ‡ Izdemir Aliaga steel plant</t>
-  </si>
-  <si>
-    <t>BatÄ±Ã§im Bornova Cement Plant</t>
-  </si>
-  <si>
     <t>YÃ¼reÄŸir Cement Plant</t>
   </si>
   <si>
     <t>CEMEX ESPAÃ‘A-ALICANTE (CEMENTO BLANCO)</t>
   </si>
   <si>
-    <t>EVERÃ‰ SAS</t>
-  </si>
-  <si>
-    <t>SÃ¶ke Cement Plant</t>
-  </si>
-  <si>
-    <t>MMK TÃ¼rkiye Metallurgical Payas plant</t>
-  </si>
-  <si>
-    <t>SarÄ±mazÄ± Cement Plant</t>
-  </si>
-  <si>
-    <t>CEMENTOS MOLINS INDUSTRIAL (SANT VICENÃ‡ DELS HORTS)</t>
+    <t>ÉVERÉ SAS</t>
   </si>
   <si>
     <t>FÃBRICA DE MONTCADA (LAFARGEHOLCIM ESPAÃ‘A SAU)</t>
@@ -538,16 +520,10 @@
     <t>CEMEX ESPAÃ‘A OPERACIONES (ALCANAR)</t>
   </si>
   <si>
-    <t>UnitÃ  Locale 3 - Impianto di Termovalorizzazione rifiuti non pericolosi</t>
-  </si>
-  <si>
     <t>FÃBRICA DE CARBONERAS (LAFARGEHOLCIM ESPAÃ‘A SAU)</t>
   </si>
   <si>
     <t>FÃBRICA DE CEMENTOS DE MÃLAGA (VOTORANTIM CEMENTOS ESPAÃ‘A, S.A.)</t>
-  </si>
-  <si>
-    <t>Proizvodnja cementa KoromaÄno</t>
   </si>
   <si>
     <t>HOLCIM ESPAÃ‘A SAU</t>
@@ -563,7 +539,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -576,13 +552,25 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -612,11 +600,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -919,8 +909,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K664"/>
+  <dimension ref="A1:K669"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="19.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.453125" customWidth="1"/>
+    <col min="5" max="5" width="29.08984375" customWidth="1"/>
+    <col min="9" max="9" width="18.08984375" customWidth="1"/>
+    <col min="11" max="11" width="17.453125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
@@ -1537,7 +1534,7 @@
         <v>19</v>
       </c>
       <c r="K18" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.35">
@@ -1811,7 +1808,7 @@
         <v>19</v>
       </c>
       <c r="K26" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.35">
@@ -2371,7 +2368,7 @@
         <v>15</v>
       </c>
       <c r="K42" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.35">
@@ -2403,7 +2400,7 @@
         <v>19</v>
       </c>
       <c r="K43" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.35">
@@ -2470,7 +2467,7 @@
         <v>19</v>
       </c>
       <c r="K45" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.35">
@@ -4565,7 +4562,7 @@
         <v>19</v>
       </c>
       <c r="K107" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.35">
@@ -4597,7 +4594,7 @@
         <v>19</v>
       </c>
       <c r="K108" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.35">
@@ -4756,14 +4753,17 @@
       <c r="G113">
         <v>23.52458</v>
       </c>
-      <c r="H113">
+      <c r="H113" s="2">
         <v>148.42871752082431</v>
       </c>
       <c r="I113" t="s">
         <v>19</v>
       </c>
+      <c r="J113" t="s">
+        <v>15</v>
+      </c>
       <c r="K113" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.35">
@@ -5331,7 +5331,7 @@
         <v>160.06924451389719</v>
       </c>
       <c r="I130" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J130" t="s">
         <v>15</v>
@@ -5366,13 +5366,13 @@
         <v>124.50625489245</v>
       </c>
       <c r="I131" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J131" t="s">
         <v>15</v>
       </c>
       <c r="K131" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.35">
@@ -5547,7 +5547,7 @@
         <v>15</v>
       </c>
       <c r="K136" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.35">
@@ -5692,7 +5692,7 @@
         <v>159</v>
       </c>
       <c r="B141" t="s">
-        <v>160</v>
+        <v>63</v>
       </c>
       <c r="C141">
         <v>38.740041689999998</v>
@@ -5701,7 +5701,7 @@
         <v>26.929011630000002</v>
       </c>
       <c r="E141" t="s">
-        <v>161</v>
+        <v>116</v>
       </c>
       <c r="F141">
         <v>38.456334730000002</v>
@@ -5716,7 +5716,7 @@
         <v>19</v>
       </c>
       <c r="K141" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.35">
@@ -5724,7 +5724,7 @@
         <v>159</v>
       </c>
       <c r="B142" t="s">
-        <v>160</v>
+        <v>63</v>
       </c>
       <c r="C142">
         <v>38.740041689999998</v>
@@ -5756,7 +5756,7 @@
         <v>159</v>
       </c>
       <c r="B143" t="s">
-        <v>160</v>
+        <v>63</v>
       </c>
       <c r="C143">
         <v>38.740041689999998</v>
@@ -5788,7 +5788,7 @@
         <v>159</v>
       </c>
       <c r="B144" t="s">
-        <v>160</v>
+        <v>63</v>
       </c>
       <c r="C144">
         <v>38.740041689999998</v>
@@ -5820,7 +5820,7 @@
         <v>159</v>
       </c>
       <c r="B145" t="s">
-        <v>160</v>
+        <v>63</v>
       </c>
       <c r="C145">
         <v>38.740041689999998</v>
@@ -5852,7 +5852,7 @@
         <v>159</v>
       </c>
       <c r="B146" t="s">
-        <v>160</v>
+        <v>63</v>
       </c>
       <c r="C146">
         <v>38.740041689999998</v>
@@ -5884,7 +5884,7 @@
         <v>159</v>
       </c>
       <c r="B147" t="s">
-        <v>160</v>
+        <v>63</v>
       </c>
       <c r="C147">
         <v>38.740041689999998</v>
@@ -6763,7 +6763,7 @@
         <v>34.761906230000001</v>
       </c>
       <c r="E174" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F174">
         <v>36.964332540000001</v>
@@ -7403,7 +7403,7 @@
         <v>-0.48333300000000001</v>
       </c>
       <c r="E194" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F194">
         <v>38.378608</v>
@@ -7662,7 +7662,7 @@
         <v>4.9366300000000001</v>
       </c>
       <c r="E202" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F202">
         <v>43.420110000000001</v>
@@ -7973,7 +7973,7 @@
         <v>159</v>
       </c>
       <c r="B212" t="s">
-        <v>161</v>
+        <v>116</v>
       </c>
       <c r="C212">
         <v>38.456334730000002</v>
@@ -8005,7 +8005,7 @@
         <v>159</v>
       </c>
       <c r="B213" t="s">
-        <v>161</v>
+        <v>116</v>
       </c>
       <c r="C213">
         <v>38.456334730000002</v>
@@ -8037,7 +8037,7 @@
         <v>159</v>
       </c>
       <c r="B214" t="s">
-        <v>161</v>
+        <v>116</v>
       </c>
       <c r="C214">
         <v>38.456334730000002</v>
@@ -8069,7 +8069,7 @@
         <v>159</v>
       </c>
       <c r="B215" t="s">
-        <v>161</v>
+        <v>116</v>
       </c>
       <c r="C215">
         <v>38.456334730000002</v>
@@ -8101,7 +8101,7 @@
         <v>159</v>
       </c>
       <c r="B216" t="s">
-        <v>161</v>
+        <v>116</v>
       </c>
       <c r="C216">
         <v>38.456334730000002</v>
@@ -8110,7 +8110,7 @@
         <v>27.26343232</v>
       </c>
       <c r="E216" t="s">
-        <v>165</v>
+        <v>51</v>
       </c>
       <c r="F216">
         <v>37.770531599999998</v>
@@ -8125,7 +8125,7 @@
         <v>19</v>
       </c>
       <c r="K216" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="217" spans="1:11" x14ac:dyDescent="0.35">
@@ -8133,7 +8133,7 @@
         <v>159</v>
       </c>
       <c r="B217" t="s">
-        <v>161</v>
+        <v>116</v>
       </c>
       <c r="C217">
         <v>38.456334730000002</v>
@@ -8142,7 +8142,7 @@
         <v>27.26343232</v>
       </c>
       <c r="E217" t="s">
-        <v>160</v>
+        <v>63</v>
       </c>
       <c r="F217">
         <v>38.740041689999998</v>
@@ -8157,7 +8157,7 @@
         <v>19</v>
       </c>
       <c r="K217" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="218" spans="1:11" x14ac:dyDescent="0.35">
@@ -8165,7 +8165,7 @@
         <v>159</v>
       </c>
       <c r="B218" t="s">
-        <v>161</v>
+        <v>116</v>
       </c>
       <c r="C218">
         <v>38.456334730000002</v>
@@ -8197,7 +8197,7 @@
         <v>159</v>
       </c>
       <c r="B219" t="s">
-        <v>161</v>
+        <v>116</v>
       </c>
       <c r="C219">
         <v>38.456334730000002</v>
@@ -8229,7 +8229,7 @@
         <v>159</v>
       </c>
       <c r="B220" t="s">
-        <v>161</v>
+        <v>116</v>
       </c>
       <c r="C220">
         <v>38.456334730000002</v>
@@ -8526,7 +8526,7 @@
         <v>35.933332999999998</v>
       </c>
       <c r="E229" t="s">
-        <v>166</v>
+        <v>115</v>
       </c>
       <c r="F229">
         <v>36.781410299999997</v>
@@ -8558,7 +8558,7 @@
         <v>35.933332999999998</v>
       </c>
       <c r="E230" t="s">
-        <v>167</v>
+        <v>27</v>
       </c>
       <c r="F230">
         <v>36.933010279999998</v>
@@ -8590,7 +8590,7 @@
         <v>35.933332999999998</v>
       </c>
       <c r="E231" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F231">
         <v>36.964332540000001</v>
@@ -9864,7 +9864,7 @@
         <v>159</v>
       </c>
       <c r="B271" t="s">
-        <v>168</v>
+        <v>128</v>
       </c>
       <c r="C271">
         <v>41.408723000000002</v>
@@ -9896,7 +9896,7 @@
         <v>159</v>
       </c>
       <c r="B272" t="s">
-        <v>168</v>
+        <v>128</v>
       </c>
       <c r="C272">
         <v>41.408723000000002</v>
@@ -9905,7 +9905,7 @@
         <v>1.9992620000000001</v>
       </c>
       <c r="E272" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="F272">
         <v>41.477659000000003</v>
@@ -9920,7 +9920,7 @@
         <v>19</v>
       </c>
       <c r="K272" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="273" spans="1:11" x14ac:dyDescent="0.35">
@@ -9928,7 +9928,7 @@
         <v>159</v>
       </c>
       <c r="B273" t="s">
-        <v>168</v>
+        <v>128</v>
       </c>
       <c r="C273">
         <v>41.408723000000002</v>
@@ -9960,7 +9960,7 @@
         <v>159</v>
       </c>
       <c r="B274" t="s">
-        <v>168</v>
+        <v>128</v>
       </c>
       <c r="C274">
         <v>41.408723000000002</v>
@@ -10001,7 +10001,7 @@
         <v>1.663019</v>
       </c>
       <c r="E275" t="s">
-        <v>168</v>
+        <v>128</v>
       </c>
       <c r="F275">
         <v>41.408723000000002</v>
@@ -10033,7 +10033,7 @@
         <v>1.663019</v>
       </c>
       <c r="E276" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="F276">
         <v>41.477659000000003</v>
@@ -10123,7 +10123,7 @@
         <v>159</v>
       </c>
       <c r="B279" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="C279">
         <v>40.578910999999998</v>
@@ -10155,7 +10155,7 @@
         <v>159</v>
       </c>
       <c r="B280" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C280">
         <v>38.378608</v>
@@ -10196,7 +10196,7 @@
         <v>27.217405800000002</v>
       </c>
       <c r="E281" t="s">
-        <v>161</v>
+        <v>116</v>
       </c>
       <c r="F281">
         <v>38.456334730000002</v>
@@ -10324,7 +10324,7 @@
         <v>27.217405800000002</v>
       </c>
       <c r="E285" t="s">
-        <v>165</v>
+        <v>51</v>
       </c>
       <c r="F285">
         <v>37.770531599999998</v>
@@ -10356,7 +10356,7 @@
         <v>27.217405800000002</v>
       </c>
       <c r="E286" t="s">
-        <v>160</v>
+        <v>63</v>
       </c>
       <c r="F286">
         <v>38.740041689999998</v>
@@ -10618,7 +10618,7 @@
         <v>14.065799999999999</v>
       </c>
       <c r="E294" t="s">
-        <v>171</v>
+        <v>121</v>
       </c>
       <c r="F294">
         <v>41.4375</v>
@@ -11008,7 +11008,7 @@
         <v>26.939949410000001</v>
       </c>
       <c r="E306" t="s">
-        <v>161</v>
+        <v>116</v>
       </c>
       <c r="F306">
         <v>38.456334730000002</v>
@@ -11139,7 +11139,7 @@
         <v>26.939949410000001</v>
       </c>
       <c r="E310" t="s">
-        <v>160</v>
+        <v>63</v>
       </c>
       <c r="F310">
         <v>38.740041689999998</v>
@@ -11395,7 +11395,7 @@
         <v>36.204844649999998</v>
       </c>
       <c r="E318" t="s">
-        <v>166</v>
+        <v>115</v>
       </c>
       <c r="F318">
         <v>36.781410299999997</v>
@@ -11427,7 +11427,7 @@
         <v>36.204844649999998</v>
       </c>
       <c r="E319" t="s">
-        <v>167</v>
+        <v>27</v>
       </c>
       <c r="F319">
         <v>36.933010279999998</v>
@@ -11459,7 +11459,7 @@
         <v>36.204844649999998</v>
       </c>
       <c r="E320" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F320">
         <v>36.964332540000001</v>
@@ -11674,7 +11674,7 @@
         <v>159</v>
       </c>
       <c r="B327" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C327">
         <v>43.420110000000001</v>
@@ -11706,7 +11706,7 @@
         <v>159</v>
       </c>
       <c r="B328" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C328">
         <v>43.420110000000001</v>
@@ -11741,7 +11741,7 @@
         <v>159</v>
       </c>
       <c r="B329" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C329">
         <v>43.420110000000001</v>
@@ -11773,7 +11773,7 @@
         <v>159</v>
       </c>
       <c r="B330" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C330">
         <v>43.420110000000001</v>
@@ -11805,7 +11805,7 @@
         <v>159</v>
       </c>
       <c r="B331" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C331">
         <v>43.420110000000001</v>
@@ -11869,7 +11869,7 @@
         <v>159</v>
       </c>
       <c r="B333" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C333">
         <v>36.966500000000003</v>
@@ -11878,7 +11878,7 @@
         <v>-1.9029</v>
       </c>
       <c r="E333" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="F333">
         <v>36.966500000000003</v>
@@ -11901,7 +11901,7 @@
         <v>159</v>
       </c>
       <c r="B334" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C334">
         <v>36.966500000000003</v>
@@ -11910,7 +11910,7 @@
         <v>-1.9029</v>
       </c>
       <c r="E334" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="F334">
         <v>36.966500000000003</v>
@@ -11933,7 +11933,7 @@
         <v>159</v>
       </c>
       <c r="B335" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="C335">
         <v>36.716600999999997</v>
@@ -11965,7 +11965,7 @@
         <v>159</v>
       </c>
       <c r="B336" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="C336">
         <v>41.477659000000003</v>
@@ -11974,7 +11974,7 @@
         <v>2.186544</v>
       </c>
       <c r="E336" t="s">
-        <v>168</v>
+        <v>128</v>
       </c>
       <c r="F336">
         <v>41.408723000000002</v>
@@ -11989,7 +11989,7 @@
         <v>19</v>
       </c>
       <c r="K336" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="337" spans="1:11" x14ac:dyDescent="0.35">
@@ -11997,7 +11997,7 @@
         <v>159</v>
       </c>
       <c r="B337" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="C337">
         <v>41.477659000000003</v>
@@ -12029,7 +12029,7 @@
         <v>159</v>
       </c>
       <c r="B338" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="C338">
         <v>41.477659000000003</v>
@@ -12061,7 +12061,7 @@
         <v>159</v>
       </c>
       <c r="B339" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="C339">
         <v>41.477659000000003</v>
@@ -12134,7 +12134,7 @@
         <v>4.8833330000000004</v>
       </c>
       <c r="E341" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F341">
         <v>43.420110000000001</v>
@@ -12425,7 +12425,7 @@
         <v>26.950319360000002</v>
       </c>
       <c r="E350" t="s">
-        <v>161</v>
+        <v>116</v>
       </c>
       <c r="F350">
         <v>38.456334730000002</v>
@@ -12556,7 +12556,7 @@
         <v>26.950319360000002</v>
       </c>
       <c r="E354" t="s">
-        <v>160</v>
+        <v>63</v>
       </c>
       <c r="F354">
         <v>38.740041689999998</v>
@@ -12687,7 +12687,7 @@
         <v>4.5322399999999998</v>
       </c>
       <c r="E358" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F358">
         <v>43.420110000000001</v>
@@ -13106,7 +13106,7 @@
         <v>13.004200000000001</v>
       </c>
       <c r="E371" t="s">
-        <v>171</v>
+        <v>121</v>
       </c>
       <c r="F371">
         <v>41.4375</v>
@@ -13153,7 +13153,7 @@
         <v>19</v>
       </c>
       <c r="K372" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="373" spans="1:11" x14ac:dyDescent="0.35">
@@ -13185,7 +13185,7 @@
         <v>19</v>
       </c>
       <c r="K373" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="374" spans="1:11" x14ac:dyDescent="0.35">
@@ -13394,7 +13394,7 @@
         <v>13.7994</v>
       </c>
       <c r="E380" t="s">
-        <v>174</v>
+        <v>49</v>
       </c>
       <c r="F380">
         <v>44.967320000000001</v>
@@ -13409,7 +13409,7 @@
         <v>19</v>
       </c>
       <c r="K380" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="381" spans="1:11" x14ac:dyDescent="0.35">
@@ -13505,7 +13505,7 @@
         <v>19</v>
       </c>
       <c r="K383" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="384" spans="1:11" x14ac:dyDescent="0.35">
@@ -13929,7 +13929,7 @@
         <v>159</v>
       </c>
       <c r="B397" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="C397">
         <v>39.666317999999997</v>
@@ -14706,7 +14706,7 @@
         <v>36.209483480000003</v>
       </c>
       <c r="E421" t="s">
-        <v>166</v>
+        <v>115</v>
       </c>
       <c r="F421">
         <v>36.781410299999997</v>
@@ -14738,7 +14738,7 @@
         <v>36.209483480000003</v>
       </c>
       <c r="E422" t="s">
-        <v>167</v>
+        <v>27</v>
       </c>
       <c r="F422">
         <v>36.933010279999998</v>
@@ -14770,7 +14770,7 @@
         <v>36.209483480000003</v>
       </c>
       <c r="E423" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F423">
         <v>36.964332540000001</v>
@@ -14930,7 +14930,7 @@
         <v>36.209483480000003</v>
       </c>
       <c r="E428" t="s">
-        <v>166</v>
+        <v>115</v>
       </c>
       <c r="F428">
         <v>36.781410299999997</v>
@@ -14962,7 +14962,7 @@
         <v>36.209483480000003</v>
       </c>
       <c r="E429" t="s">
-        <v>167</v>
+        <v>27</v>
       </c>
       <c r="F429">
         <v>36.933010279999998</v>
@@ -14994,7 +14994,7 @@
         <v>36.209483480000003</v>
       </c>
       <c r="E430" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F430">
         <v>36.964332540000001</v>
@@ -15250,7 +15250,7 @@
         <v>27.133333</v>
       </c>
       <c r="E438" t="s">
-        <v>161</v>
+        <v>116</v>
       </c>
       <c r="F438">
         <v>38.456334730000002</v>
@@ -15413,7 +15413,7 @@
         <v>27.133333</v>
       </c>
       <c r="E443" t="s">
-        <v>165</v>
+        <v>51</v>
       </c>
       <c r="F443">
         <v>37.770531599999998</v>
@@ -15445,7 +15445,7 @@
         <v>27.133333</v>
       </c>
       <c r="E444" t="s">
-        <v>160</v>
+        <v>63</v>
       </c>
       <c r="F444">
         <v>38.740041689999998</v>
@@ -15541,7 +15541,7 @@
         <v>26.961168740000002</v>
       </c>
       <c r="E447" t="s">
-        <v>161</v>
+        <v>116</v>
       </c>
       <c r="F447">
         <v>38.456334730000002</v>
@@ -15675,7 +15675,7 @@
         <v>26.961168740000002</v>
       </c>
       <c r="E451" t="s">
-        <v>160</v>
+        <v>63</v>
       </c>
       <c r="F451">
         <v>38.740041689999998</v>
@@ -15934,7 +15934,7 @@
         <v>14.118499999999999</v>
       </c>
       <c r="E459" t="s">
-        <v>174</v>
+        <v>49</v>
       </c>
       <c r="F459">
         <v>44.967320000000001</v>
@@ -15998,7 +15998,7 @@
         <v>27.25</v>
       </c>
       <c r="E461" t="s">
-        <v>161</v>
+        <v>116</v>
       </c>
       <c r="F461">
         <v>38.456334730000002</v>
@@ -16094,7 +16094,7 @@
         <v>27.25</v>
       </c>
       <c r="E464" t="s">
-        <v>165</v>
+        <v>51</v>
       </c>
       <c r="F464">
         <v>37.770531599999998</v>
@@ -16702,7 +16702,7 @@
         <v>-4.4166670000000003</v>
       </c>
       <c r="E483" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="F483">
         <v>36.716600999999997</v>
@@ -16781,7 +16781,7 @@
         <v>19</v>
       </c>
       <c r="K485" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="486" spans="1:11" x14ac:dyDescent="0.35">
@@ -16830,7 +16830,7 @@
         <v>34.633333</v>
       </c>
       <c r="E487" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F487">
         <v>36.964332540000001</v>
@@ -16885,7 +16885,7 @@
         <v>159</v>
       </c>
       <c r="B489" t="s">
-        <v>166</v>
+        <v>115</v>
       </c>
       <c r="C489">
         <v>36.781410299999997</v>
@@ -16917,7 +16917,7 @@
         <v>159</v>
       </c>
       <c r="B490" t="s">
-        <v>166</v>
+        <v>115</v>
       </c>
       <c r="C490">
         <v>36.781410299999997</v>
@@ -16949,7 +16949,7 @@
         <v>159</v>
       </c>
       <c r="B491" t="s">
-        <v>166</v>
+        <v>115</v>
       </c>
       <c r="C491">
         <v>36.781410299999997</v>
@@ -16958,7 +16958,7 @@
         <v>36.205645199999999</v>
       </c>
       <c r="E491" t="s">
-        <v>167</v>
+        <v>27</v>
       </c>
       <c r="F491">
         <v>36.933010279999998</v>
@@ -16973,7 +16973,7 @@
         <v>19</v>
       </c>
       <c r="K491" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="492" spans="1:11" x14ac:dyDescent="0.35">
@@ -16981,7 +16981,7 @@
         <v>159</v>
       </c>
       <c r="B492" t="s">
-        <v>166</v>
+        <v>115</v>
       </c>
       <c r="C492">
         <v>36.781410299999997</v>
@@ -16990,7 +16990,7 @@
         <v>36.205645199999999</v>
       </c>
       <c r="E492" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F492">
         <v>36.964332540000001</v>
@@ -17005,7 +17005,7 @@
         <v>19</v>
       </c>
       <c r="K492" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="493" spans="1:11" x14ac:dyDescent="0.35">
@@ -17013,7 +17013,7 @@
         <v>159</v>
       </c>
       <c r="B493" t="s">
-        <v>166</v>
+        <v>115</v>
       </c>
       <c r="C493">
         <v>36.781410299999997</v>
@@ -17045,7 +17045,7 @@
         <v>159</v>
       </c>
       <c r="B494" t="s">
-        <v>166</v>
+        <v>115</v>
       </c>
       <c r="C494">
         <v>36.781410299999997</v>
@@ -17342,7 +17342,7 @@
         <v>14.275</v>
       </c>
       <c r="E503" t="s">
-        <v>171</v>
+        <v>121</v>
       </c>
       <c r="F503">
         <v>41.4375</v>
@@ -17377,7 +17377,7 @@
         <v>26.916667</v>
       </c>
       <c r="E504" t="s">
-        <v>161</v>
+        <v>116</v>
       </c>
       <c r="F504">
         <v>38.456334730000002</v>
@@ -17537,7 +17537,7 @@
         <v>26.916667</v>
       </c>
       <c r="E509" t="s">
-        <v>160</v>
+        <v>63</v>
       </c>
       <c r="F509">
         <v>38.740041689999998</v>
@@ -17633,7 +17633,7 @@
         <v>2.2298369999999998</v>
       </c>
       <c r="E512" t="s">
-        <v>168</v>
+        <v>128</v>
       </c>
       <c r="F512">
         <v>41.408723000000002</v>
@@ -17700,7 +17700,7 @@
         <v>2.2298369999999998</v>
       </c>
       <c r="E514" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="F514">
         <v>41.477659000000003</v>
@@ -18302,7 +18302,7 @@
         <v>159</v>
       </c>
       <c r="B533" t="s">
-        <v>174</v>
+        <v>49</v>
       </c>
       <c r="C533">
         <v>44.967320000000001</v>
@@ -18326,7 +18326,7 @@
         <v>19</v>
       </c>
       <c r="K533" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="534" spans="1:11" x14ac:dyDescent="0.35">
@@ -18334,7 +18334,7 @@
         <v>159</v>
       </c>
       <c r="B534" t="s">
-        <v>174</v>
+        <v>49</v>
       </c>
       <c r="C534">
         <v>44.967320000000001</v>
@@ -18366,7 +18366,7 @@
         <v>159</v>
       </c>
       <c r="B535" t="s">
-        <v>174</v>
+        <v>49</v>
       </c>
       <c r="C535">
         <v>44.967320000000001</v>
@@ -18526,7 +18526,7 @@
         <v>159</v>
       </c>
       <c r="B540" t="s">
-        <v>165</v>
+        <v>51</v>
       </c>
       <c r="C540">
         <v>37.770531599999998</v>
@@ -18535,7 +18535,7 @@
         <v>27.437213499999999</v>
       </c>
       <c r="E540" t="s">
-        <v>161</v>
+        <v>116</v>
       </c>
       <c r="F540">
         <v>38.456334730000002</v>
@@ -18550,7 +18550,7 @@
         <v>19</v>
       </c>
       <c r="K540" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="541" spans="1:11" x14ac:dyDescent="0.35">
@@ -18558,7 +18558,7 @@
         <v>159</v>
       </c>
       <c r="B541" t="s">
-        <v>165</v>
+        <v>51</v>
       </c>
       <c r="C541">
         <v>37.770531599999998</v>
@@ -18590,7 +18590,7 @@
         <v>159</v>
       </c>
       <c r="B542" t="s">
-        <v>165</v>
+        <v>51</v>
       </c>
       <c r="C542">
         <v>37.770531599999998</v>
@@ -18622,7 +18622,7 @@
         <v>159</v>
       </c>
       <c r="B543" t="s">
-        <v>165</v>
+        <v>51</v>
       </c>
       <c r="C543">
         <v>37.770531599999998</v>
@@ -18663,7 +18663,7 @@
         <v>-0.216667</v>
       </c>
       <c r="E544" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="F544">
         <v>39.666317999999997</v>
@@ -18686,7 +18686,7 @@
         <v>159</v>
       </c>
       <c r="B545" t="s">
-        <v>167</v>
+        <v>27</v>
       </c>
       <c r="C545">
         <v>36.933010279999998</v>
@@ -18718,7 +18718,7 @@
         <v>159</v>
       </c>
       <c r="B546" t="s">
-        <v>167</v>
+        <v>27</v>
       </c>
       <c r="C546">
         <v>36.933010279999998</v>
@@ -18750,7 +18750,7 @@
         <v>159</v>
       </c>
       <c r="B547" t="s">
-        <v>167</v>
+        <v>27</v>
       </c>
       <c r="C547">
         <v>36.933010279999998</v>
@@ -18759,7 +18759,7 @@
         <v>36.003987639999998</v>
       </c>
       <c r="E547" t="s">
-        <v>166</v>
+        <v>115</v>
       </c>
       <c r="F547">
         <v>36.781410299999997</v>
@@ -18774,7 +18774,7 @@
         <v>19</v>
       </c>
       <c r="K547" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="548" spans="1:11" x14ac:dyDescent="0.35">
@@ -18782,7 +18782,7 @@
         <v>159</v>
       </c>
       <c r="B548" t="s">
-        <v>167</v>
+        <v>27</v>
       </c>
       <c r="C548">
         <v>36.933010279999998</v>
@@ -18791,7 +18791,7 @@
         <v>36.003987639999998</v>
       </c>
       <c r="E548" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F548">
         <v>36.964332540000001</v>
@@ -18806,7 +18806,7 @@
         <v>19</v>
       </c>
       <c r="K548" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="549" spans="1:11" x14ac:dyDescent="0.35">
@@ -18814,7 +18814,7 @@
         <v>159</v>
       </c>
       <c r="B549" t="s">
-        <v>167</v>
+        <v>27</v>
       </c>
       <c r="C549">
         <v>36.933010279999998</v>
@@ -18846,7 +18846,7 @@
         <v>159</v>
       </c>
       <c r="B550" t="s">
-        <v>167</v>
+        <v>27</v>
       </c>
       <c r="C550">
         <v>36.933010279999998</v>
@@ -19306,7 +19306,7 @@
         <v>1.233333</v>
       </c>
       <c r="E564" t="s">
-        <v>168</v>
+        <v>128</v>
       </c>
       <c r="F564">
         <v>41.408723000000002</v>
@@ -19370,7 +19370,7 @@
         <v>1.233333</v>
       </c>
       <c r="E566" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="F566">
         <v>40.578910999999998</v>
@@ -19402,7 +19402,7 @@
         <v>1.233333</v>
       </c>
       <c r="E567" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="F567">
         <v>41.477659000000003</v>
@@ -20013,7 +20013,7 @@
         <v>14.388299999999999</v>
       </c>
       <c r="E586" t="s">
-        <v>171</v>
+        <v>121</v>
       </c>
       <c r="F586">
         <v>41.4375</v>
@@ -20095,7 +20095,7 @@
         <v>19</v>
       </c>
       <c r="K588" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="589" spans="1:11" x14ac:dyDescent="0.35">
@@ -20159,7 +20159,7 @@
         <v>19</v>
       </c>
       <c r="K590" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="591" spans="1:11" x14ac:dyDescent="0.35">
@@ -20191,7 +20191,7 @@
         <v>19</v>
       </c>
       <c r="K591" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="592" spans="1:11" x14ac:dyDescent="0.35">
@@ -20223,7 +20223,7 @@
         <v>19</v>
       </c>
       <c r="K592" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="593" spans="1:11" x14ac:dyDescent="0.35">
@@ -20255,7 +20255,7 @@
         <v>19</v>
       </c>
       <c r="K593" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="594" spans="1:11" x14ac:dyDescent="0.35">
@@ -20304,7 +20304,7 @@
         <v>5.9166670000000003</v>
       </c>
       <c r="E595" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F595">
         <v>43.420110000000001</v>
@@ -20479,7 +20479,7 @@
         <v>19</v>
       </c>
       <c r="K600" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="601" spans="1:11" x14ac:dyDescent="0.35">
@@ -20496,7 +20496,7 @@
         <v>13.802586</v>
       </c>
       <c r="E601" t="s">
-        <v>174</v>
+        <v>49</v>
       </c>
       <c r="F601">
         <v>44.967320000000001</v>
@@ -21159,7 +21159,7 @@
         <v>159</v>
       </c>
       <c r="B622" t="s">
-        <v>171</v>
+        <v>121</v>
       </c>
       <c r="C622">
         <v>41.4375</v>
@@ -21191,7 +21191,7 @@
         <v>159</v>
       </c>
       <c r="B623" t="s">
-        <v>171</v>
+        <v>121</v>
       </c>
       <c r="C623">
         <v>41.4375</v>
@@ -21223,7 +21223,7 @@
         <v>159</v>
       </c>
       <c r="B624" t="s">
-        <v>171</v>
+        <v>121</v>
       </c>
       <c r="C624">
         <v>41.4375</v>
@@ -21255,7 +21255,7 @@
         <v>159</v>
       </c>
       <c r="B625" t="s">
-        <v>171</v>
+        <v>121</v>
       </c>
       <c r="C625">
         <v>41.4375</v>
@@ -21383,7 +21383,7 @@
         <v>159</v>
       </c>
       <c r="B629" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C629">
         <v>36.964332540000001</v>
@@ -21415,7 +21415,7 @@
         <v>159</v>
       </c>
       <c r="B630" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C630">
         <v>36.964332540000001</v>
@@ -21447,7 +21447,7 @@
         <v>159</v>
       </c>
       <c r="B631" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C631">
         <v>36.964332540000001</v>
@@ -21479,7 +21479,7 @@
         <v>159</v>
       </c>
       <c r="B632" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C632">
         <v>36.964332540000001</v>
@@ -21488,7 +21488,7 @@
         <v>35.452228929999997</v>
       </c>
       <c r="E632" t="s">
-        <v>166</v>
+        <v>115</v>
       </c>
       <c r="F632">
         <v>36.781410299999997</v>
@@ -21503,7 +21503,7 @@
         <v>19</v>
       </c>
       <c r="K632" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="633" spans="1:11" x14ac:dyDescent="0.35">
@@ -21511,7 +21511,7 @@
         <v>159</v>
       </c>
       <c r="B633" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C633">
         <v>36.964332540000001</v>
@@ -21520,7 +21520,7 @@
         <v>35.452228929999997</v>
       </c>
       <c r="E633" t="s">
-        <v>167</v>
+        <v>27</v>
       </c>
       <c r="F633">
         <v>36.933010279999998</v>
@@ -21535,7 +21535,7 @@
         <v>19</v>
       </c>
       <c r="K633" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="634" spans="1:11" x14ac:dyDescent="0.35">
@@ -21543,7 +21543,7 @@
         <v>159</v>
       </c>
       <c r="B634" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C634">
         <v>36.964332540000001</v>
@@ -21575,7 +21575,7 @@
         <v>159</v>
       </c>
       <c r="B635" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C635">
         <v>36.964332540000001</v>
@@ -21607,7 +21607,7 @@
         <v>159</v>
       </c>
       <c r="B636" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C636">
         <v>36.964332540000001</v>
@@ -21680,7 +21680,7 @@
         <v>5.93276</v>
       </c>
       <c r="E638" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F638">
         <v>43.420110000000001</v>
@@ -21799,7 +21799,7 @@
         <v>159</v>
       </c>
       <c r="B642" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="C642">
         <v>39.022463000000002</v>
@@ -22003,7 +22003,7 @@
         <v>23.52458</v>
       </c>
       <c r="E648" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="F648">
         <v>37.96</v>
@@ -22015,10 +22015,13 @@
         <v>21.742702199965091</v>
       </c>
       <c r="I648" t="s">
-        <v>19</v>
+        <v>14</v>
+      </c>
+      <c r="J648" t="s">
+        <v>15</v>
       </c>
       <c r="K648" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="649" spans="1:11" x14ac:dyDescent="0.35">
@@ -22572,8 +22575,171 @@
         <v>14</v>
       </c>
     </row>
+    <row r="665" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A665" t="s">
+        <v>159</v>
+      </c>
+      <c r="B665" t="s">
+        <v>89</v>
+      </c>
+      <c r="C665">
+        <v>38.335569999999997</v>
+      </c>
+      <c r="D665">
+        <v>21.84543</v>
+      </c>
+      <c r="E665" t="s">
+        <v>169</v>
+      </c>
+      <c r="F665">
+        <v>37.96</v>
+      </c>
+      <c r="G665">
+        <v>23.4023</v>
+      </c>
+      <c r="H665" s="3">
+        <v>157.51</v>
+      </c>
+      <c r="I665" t="s">
+        <v>14</v>
+      </c>
+      <c r="J665" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="666" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A666" t="s">
+        <v>159</v>
+      </c>
+      <c r="B666" t="s">
+        <v>42</v>
+      </c>
+      <c r="C666">
+        <v>39.351709999999997</v>
+      </c>
+      <c r="D666">
+        <v>22.984500000000001</v>
+      </c>
+      <c r="E666" t="s">
+        <v>55</v>
+      </c>
+      <c r="F666">
+        <v>38.130180000000003</v>
+      </c>
+      <c r="G666">
+        <v>23.52458</v>
+      </c>
+      <c r="H666">
+        <v>226.2</v>
+      </c>
+      <c r="I666" t="s">
+        <v>14</v>
+      </c>
+      <c r="J666" t="s">
+        <v>15</v>
+      </c>
+      <c r="K666" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="667" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A667" t="s">
+        <v>159</v>
+      </c>
+      <c r="B667" t="s">
+        <v>42</v>
+      </c>
+      <c r="C667">
+        <v>39.351709999999997</v>
+      </c>
+      <c r="D667">
+        <v>22.984500000000001</v>
+      </c>
+      <c r="E667" t="s">
+        <v>169</v>
+      </c>
+      <c r="F667">
+        <v>37.96</v>
+      </c>
+      <c r="G667">
+        <v>23.4023</v>
+      </c>
+      <c r="H667" s="3">
+        <v>253.78</v>
+      </c>
+      <c r="I667" t="s">
+        <v>19</v>
+      </c>
+      <c r="J667" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="668" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A668" t="s">
+        <v>159</v>
+      </c>
+      <c r="B668" t="s">
+        <v>87</v>
+      </c>
+      <c r="C668">
+        <v>40.699100000000001</v>
+      </c>
+      <c r="D668">
+        <v>22.953199999999999</v>
+      </c>
+      <c r="E668" t="s">
+        <v>42</v>
+      </c>
+      <c r="F668">
+        <v>39.351709999999997</v>
+      </c>
+      <c r="G668">
+        <v>22.984500000000001</v>
+      </c>
+      <c r="H668" s="3">
+        <v>216.25</v>
+      </c>
+      <c r="I668" t="s">
+        <v>14</v>
+      </c>
+      <c r="J668" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="669" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A669" t="s">
+        <v>159</v>
+      </c>
+      <c r="B669" t="s">
+        <v>81</v>
+      </c>
+      <c r="C669">
+        <v>40.5167</v>
+      </c>
+      <c r="D669">
+        <v>17.1999</v>
+      </c>
+      <c r="E669" t="s">
+        <v>147</v>
+      </c>
+      <c r="F669">
+        <v>39.078000000000003</v>
+      </c>
+      <c r="G669">
+        <v>17.135999999999999</v>
+      </c>
+      <c r="H669" s="3">
+        <v>236.6</v>
+      </c>
+      <c r="I669" t="s">
+        <v>14</v>
+      </c>
+      <c r="J669" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K664" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:K669" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>